--- a/方案设计/文件夹/项目/全渠道管报/验证/管报费用项业务验证地图.xlsx
+++ b/方案设计/文件夹/项目/全渠道管报/验证/管报费用项业务验证地图.xlsx
@@ -10,12 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-怎么用" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-验证包总览" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-费用项×渠道地图" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-时间节点" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-验证包总览'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02-费用项×渠道地图'!$A$1:$V$257</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04-时间节点'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -694,11 +692,7 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>04-时间节点：即日起–9/22 由 FBA 和产品预验证；研发 9/23 交完整被验数。最迟 10/16 收口。中秋 9/25–27、国庆 10/1–7 不安排测试。</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n"/>
@@ -27106,358 +27100,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>节点</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>工作日说明</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>做什么</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>责任人</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>FBA + 产品预验证</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>即日起–9/22（二）</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>工作日（含 9/20 调休，但 9/20 不排测试）</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>FBA 先验亚马逊平台报告能对的项（A 包）；产品拆包、对齐口径和对照组页面。此阶段不依赖研发完整底表。</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>FBA、产品</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>9/22 前完成预验证结论；缺完整被验数的项标「待 9/23 对数」</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>研发交完整被验数</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>9/23（三）</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>工作日，中秋前</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>交出 7 月、8 月完整「MSKU店铺费用明细」+ 汇总，两月分开</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>研发</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>完整被验数以此日为准；产品当天发到各包</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>完整数据对齐 / FBA 复核</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>9/23–9/24</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>工作日</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>产品把底表拆进各验证包；FBA 用完整被验数复核 A 包</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>产品、FBA</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>中秋前只收 A 包和产品侧结论，不要求全渠道填完</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>中秋停测</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>9/25–9/27</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>中秋放假，不安排测试</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>周五至周日放假</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>各包填对照（国庆前）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>9/28–9/30</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>工作日</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>对照完整被验数填对照金额；渠道运营完成 B3、D；G 先对量级</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>渠道运营为主</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>国庆前收一版，不要求全部关闭差异</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>国庆停测</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>10/1–10/7</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>国庆放假调休，不安排测试</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>7 天假期，不要预留节假日加班对账</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>差异评审</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>10/8–10/9</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>节后工作日</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>只看超阈值或讲不清的行；三选一写死：认系统 / 改口径 / 本期不进管报</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>产品主持；G 包渠道运营+财务一起</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>10/10 周六调休上班，不排测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>改口径回写 + 抽测</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>10/12–10/15</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>工作日</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>改过的口径回写钉钉表；抽测复验</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>产品 / 研发 / 对应责任人</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>只复验改过的项，不要重开全量</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>最迟收口</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>10/16（五）</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>工作日，硬节点</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>全部包有结论；未关闭项写明本期不进管报或遗留清单</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>产品汇总</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>超过此日不再为验证扩期</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>说明：9/22 前由 FBA 和产品先验；研发 9/23 提供完整被验数。日历按国务院 2026 年放假安排：中秋 9/25–27，国庆 10/1–7；9/20、10/10 调休上班但不排测试。样本月仍是已关账 2026-07、未关账 2026-08。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F10"/>
-  <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>